--- a/jpcore-r4/feature/ImagingStudyTest/StructureDefinition-jp-observation-microbiology.xlsx
+++ b/jpcore-r4/feature/ImagingStudyTest/StructureDefinition-jp-observation-microbiology.xlsx
@@ -282,7 +282,7 @@
   </si>
   <si>
     <t>dom-2:リソースが別のリソースに含まれている場合、ネストされたリソースを含めてはなりません / If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidまたはmeta.lastupdatedを持たないものとします / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が必要です / A resource should have narrative for robust management {text.`div`.exists()}obs-6:databsentrasonは、観察.value [x]が存在しない場合にのみ存在するものとします / dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}obs-7:visserveration.codeがvisserveration.component.codeと同じ場合、コードに関連付けられている値要素が存在しないでください / If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}</t>
+dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が必要です / A resource should have narrative for robust management {text.`div`.exists()}obs-6:databsentrasonは、観察.value [x]が存在しない場合にのみ存在するものとします / dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}obs-7:visserveration.codeがvisserveration.component.codeと同じ場合、コードに関連付けられている値要素が存在しないでください / If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}</t>
   </si>
   <si>
     <t>Event</t>
@@ -329,16 +329,16 @@
 </t>
   </si>
   <si>
-    <t>リソースに関するメタデータ / Metadata about the resource</t>
-  </si>
-  <si>
-    <t>リソースに関するメタデータ。これは、インフラストラクチャによって維持されるコンテンツです。コンテンツの変更は、常にリソースのバージョンの変更に関連付けられているとは限りません。 / The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
+    <t>リソースに関するMetadata / Metadata about the resource</t>
+  </si>
+  <si>
+    <t>リソースに関するMetadata。これは、インフラストラクチャによって維持されるコンテンツです。コンテンツの変更は、常にリソースのバージョンの変更に関連付けられているとは限りません。 / The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
   </si>
   <si>
     <t>Resource.meta</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 </t>
   </si>
   <si>
@@ -464,7 +464,7 @@
     <t>DomainResource.extension</t>
   </si>
   <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 ext-1:両方ではなく、拡張または値[x]が必要です / Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
@@ -1598,7 +1598,7 @@
     <t>どの値が「正常」と見なされるかを知ることは、特定の結果の意義を評価するのに役立つ。さまざまなコンテキストに対応するため複数の参照範囲を提供できる必要がある。</t>
   </si>
   <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 obs-3:少なくとも低いまたは高またはテキストが必要です / Must have at least a low or a high or text {low.exists() or high.exists() or text.exists()}</t>
   </si>
   <si>

--- a/jpcore-r4/feature/ImagingStudyTest/StructureDefinition-jp-observation-microbiology.xlsx
+++ b/jpcore-r4/feature/ImagingStudyTest/StructureDefinition-jp-observation-microbiology.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4444" uniqueCount="601">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4445" uniqueCount="602">
   <si>
     <t>Property</t>
   </si>
@@ -621,7 +621,10 @@
     <t>どの観測値が取得されて表示されるかをフィルタリングするために使用されます。 / Used for filtering what observations are retrieved and displayed.</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_SimpleObservationCategory_VS</t>
+    <t>高レベルの観測カテゴリのコード。 / Codes for high level observation categories.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/observation-category</t>
   </si>
   <si>
     <t xml:space="preserve">value:coding.system}
@@ -646,7 +649,10 @@
     <t>このObservationに関する分類（JP_SimpleObservationCategory_VS）、必須項目</t>
   </si>
   <si>
-    <t>階層的にカテゴリーを設定することで粒度のレベルを概念定義できる。</t>
+    <t>必要なカテゴリバリューセットに加えて、この要素は、所有者のカテゴリの定義に基づいてさまざまな分類スキームを許可し、効果的に複数のカテゴリを一度に使用できます。粒度のレベルは、値セットのカテゴリの概念によって定義されます。 / In addition to the required category valueset, this element allows various categorization schemes based on the owner’s definition of the category and effectively multiple categories can be used at once.  The level of granularity is defined by the category concepts in the value set.</t>
+  </si>
+  <si>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_SimpleObservationCategory_VS</t>
   </si>
   <si>
     <t>Observation.category:first.id</t>
@@ -902,10 +908,10 @@
     <t>second</t>
   </si>
   <si>
-    <t>このObservationに関するLOINC上の分類、任意項目</t>
-  </si>
-  <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ObservationCategory_Microbiology_VS</t>
+    <t>第2カテゴリはLOINCのコード18725-2固定とする、ValueSetは指定しない</t>
+  </si>
+  <si>
+    <t>階層的にカテゴリーを設定することで粒度のレベルを概念定義できる。</t>
   </si>
   <si>
     <t>Observation.category:second.id</t>
@@ -1490,10 +1496,7 @@
 If the use case requires BodySite to be handled as a separate resource (e.g. to identify and track separately) then use the standard extension[ bodySite](http://hl7.org/fhir/R4/extension-bodysite.html).</t>
   </si>
   <si>
-    <t>解剖学的場所を説明するコード。左右性が含まれる場合があります。 / Codes describing anatomical locations. May include laterality.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/body-site</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_Observation_BodySite_VS</t>
   </si>
   <si>
     <t>&lt; 123037004 |Body structure|</t>
@@ -2222,7 +2225,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="105.8828125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="69.40234375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="66.27734375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
@@ -3999,22 +4002,24 @@
       <c r="X15" t="s" s="2">
         <v>118</v>
       </c>
-      <c r="Y15" s="2"/>
+      <c r="Y15" t="s" s="2">
+        <v>194</v>
+      </c>
       <c r="Z15" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AB15" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AC15" s="2"/>
       <c r="AD15" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE15" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AF15" t="s" s="2">
         <v>188</v>
@@ -4041,10 +4046,10 @@
         <v>83</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AO15" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AP15" t="s" s="2">
         <v>83</v>
@@ -4052,13 +4057,13 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B16" t="s" s="2">
         <v>188</v>
       </c>
       <c r="C16" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D16" t="s" s="2">
         <v>83</v>
@@ -4068,7 +4073,7 @@
         <v>94</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>83</v>
@@ -4083,13 +4088,13 @@
         <v>190</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="O16" t="s" s="2">
         <v>193</v>
@@ -4121,7 +4126,7 @@
       </c>
       <c r="Y16" s="2"/>
       <c r="Z16" t="s" s="2">
-        <v>194</v>
+        <v>204</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>83</v>
@@ -4163,10 +4168,10 @@
         <v>83</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AP16" t="s" s="2">
         <v>83</v>
@@ -4174,10 +4179,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4200,13 +4205,13 @@
         <v>83</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -4257,7 +4262,7 @@
         <v>83</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>81</v>
@@ -4281,7 +4286,7 @@
         <v>83</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>83</v>
@@ -4292,10 +4297,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4324,7 +4329,7 @@
         <v>141</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="N18" t="s" s="2">
         <v>143</v>
@@ -4365,19 +4370,19 @@
         <v>83</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>81</v>
@@ -4401,7 +4406,7 @@
         <v>83</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>83</v>
@@ -4412,10 +4417,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4438,19 +4443,19 @@
         <v>95</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>83</v>
@@ -4499,7 +4504,7 @@
         <v>83</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>81</v>
@@ -4520,10 +4525,10 @@
         <v>83</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>83</v>
@@ -4534,10 +4539,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4560,13 +4565,13 @@
         <v>83</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -4617,7 +4622,7 @@
         <v>83</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>81</v>
@@ -4641,7 +4646,7 @@
         <v>83</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>83</v>
@@ -4652,10 +4657,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4684,7 +4689,7 @@
         <v>141</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="N21" t="s" s="2">
         <v>143</v>
@@ -4725,19 +4730,19 @@
         <v>83</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="AC21" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="AD21" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>81</v>
@@ -4761,7 +4766,7 @@
         <v>83</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="AO21" t="s" s="2">
         <v>83</v>
@@ -4772,10 +4777,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4801,23 +4806,23 @@
         <v>108</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q22" s="2"/>
       <c r="R22" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="S22" t="s" s="2">
         <v>83</v>
@@ -4859,7 +4864,7 @@
         <v>83</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>81</v>
@@ -4880,10 +4885,10 @@
         <v>83</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>83</v>
@@ -4894,10 +4899,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4920,16 +4925,16 @@
         <v>95</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4979,7 +4984,7 @@
         <v>83</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>81</v>
@@ -5000,10 +5005,10 @@
         <v>83</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>83</v>
@@ -5014,10 +5019,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -5043,21 +5048,21 @@
         <v>114</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q24" s="2"/>
       <c r="R24" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="S24" t="s" s="2">
         <v>83</v>
@@ -5099,7 +5104,7 @@
         <v>83</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>81</v>
@@ -5120,10 +5125,10 @@
         <v>83</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>83</v>
@@ -5134,10 +5139,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5160,17 +5165,17 @@
         <v>95</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>83</v>
@@ -5219,7 +5224,7 @@
         <v>83</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>81</v>
@@ -5240,10 +5245,10 @@
         <v>83</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>83</v>
@@ -5254,10 +5259,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5280,19 +5285,19 @@
         <v>95</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>83</v>
@@ -5341,7 +5346,7 @@
         <v>83</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>81</v>
@@ -5362,10 +5367,10 @@
         <v>83</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>83</v>
@@ -5376,10 +5381,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5402,19 +5407,19 @@
         <v>95</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>83</v>
@@ -5463,7 +5468,7 @@
         <v>83</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>81</v>
@@ -5484,10 +5489,10 @@
         <v>83</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>83</v>
@@ -5498,13 +5503,13 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="B28" t="s" s="2">
         <v>188</v>
       </c>
       <c r="C28" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="D28" t="s" s="2">
         <v>83</v>
@@ -5529,13 +5534,13 @@
         <v>190</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>202</v>
+        <v>289</v>
       </c>
       <c r="O28" t="s" s="2">
         <v>193</v>
@@ -5565,9 +5570,11 @@
       <c r="X28" t="s" s="2">
         <v>118</v>
       </c>
-      <c r="Y28" s="2"/>
+      <c r="Y28" t="s" s="2">
+        <v>194</v>
+      </c>
       <c r="Z28" t="s" s="2">
-        <v>287</v>
+        <v>195</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>83</v>
@@ -5609,10 +5616,10 @@
         <v>83</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AP28" t="s" s="2">
         <v>83</v>
@@ -5620,10 +5627,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5646,13 +5653,13 @@
         <v>83</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -5703,7 +5710,7 @@
         <v>83</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>81</v>
@@ -5727,7 +5734,7 @@
         <v>83</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>83</v>
@@ -5738,10 +5745,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5770,7 +5777,7 @@
         <v>141</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="N30" t="s" s="2">
         <v>143</v>
@@ -5811,19 +5818,19 @@
         <v>83</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="AC30" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="AD30" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>81</v>
@@ -5847,7 +5854,7 @@
         <v>83</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>83</v>
@@ -5858,10 +5865,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5884,19 +5891,19 @@
         <v>95</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>83</v>
@@ -5945,7 +5952,7 @@
         <v>83</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>81</v>
@@ -5966,10 +5973,10 @@
         <v>83</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>83</v>
@@ -5980,10 +5987,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6006,13 +6013,13 @@
         <v>83</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -6063,7 +6070,7 @@
         <v>83</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>81</v>
@@ -6087,7 +6094,7 @@
         <v>83</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>83</v>
@@ -6098,10 +6105,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6130,7 +6137,7 @@
         <v>141</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="N33" t="s" s="2">
         <v>143</v>
@@ -6171,19 +6178,19 @@
         <v>83</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="AC33" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="AD33" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>81</v>
@@ -6207,7 +6214,7 @@
         <v>83</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>83</v>
@@ -6218,10 +6225,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6247,23 +6254,23 @@
         <v>108</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q34" s="2"/>
       <c r="R34" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="S34" t="s" s="2">
         <v>83</v>
@@ -6305,7 +6312,7 @@
         <v>83</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>81</v>
@@ -6326,10 +6333,10 @@
         <v>83</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>83</v>
@@ -6340,10 +6347,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6366,16 +6373,16 @@
         <v>95</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -6425,7 +6432,7 @@
         <v>83</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>81</v>
@@ -6446,10 +6453,10 @@
         <v>83</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>83</v>
@@ -6460,10 +6467,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6489,21 +6496,21 @@
         <v>114</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q36" s="2"/>
       <c r="R36" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="S36" t="s" s="2">
         <v>83</v>
@@ -6545,7 +6552,7 @@
         <v>83</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>81</v>
@@ -6566,10 +6573,10 @@
         <v>83</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>83</v>
@@ -6580,10 +6587,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6606,17 +6613,17 @@
         <v>95</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>83</v>
@@ -6626,7 +6633,7 @@
         <v>83</v>
       </c>
       <c r="S37" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="T37" t="s" s="2">
         <v>83</v>
@@ -6665,7 +6672,7 @@
         <v>83</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>81</v>
@@ -6686,10 +6693,10 @@
         <v>83</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>83</v>
@@ -6700,10 +6707,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6726,19 +6733,19 @@
         <v>95</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>83</v>
@@ -6787,7 +6794,7 @@
         <v>83</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>81</v>
@@ -6808,10 +6815,10 @@
         <v>83</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>83</v>
@@ -6822,10 +6829,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6848,19 +6855,19 @@
         <v>95</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>83</v>
@@ -6909,7 +6916,7 @@
         <v>83</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>81</v>
@@ -6930,10 +6937,10 @@
         <v>83</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>83</v>
@@ -6944,13 +6951,13 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="B40" t="s" s="2">
         <v>188</v>
       </c>
       <c r="C40" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="D40" t="s" s="2">
         <v>83</v>
@@ -6975,13 +6982,13 @@
         <v>190</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>202</v>
+        <v>289</v>
       </c>
       <c r="O40" t="s" s="2">
         <v>193</v>
@@ -7013,7 +7020,7 @@
       </c>
       <c r="Y40" s="2"/>
       <c r="Z40" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>83</v>
@@ -7055,10 +7062,10 @@
         <v>83</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AP40" t="s" s="2">
         <v>83</v>
@@ -7066,10 +7073,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7092,13 +7099,13 @@
         <v>83</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -7149,7 +7156,7 @@
         <v>83</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>81</v>
@@ -7173,7 +7180,7 @@
         <v>83</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>83</v>
@@ -7184,10 +7191,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7216,7 +7223,7 @@
         <v>141</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="N42" t="s" s="2">
         <v>143</v>
@@ -7257,19 +7264,19 @@
         <v>83</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="AC42" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="AD42" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>81</v>
@@ -7293,7 +7300,7 @@
         <v>83</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>83</v>
@@ -7304,10 +7311,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7330,19 +7337,19 @@
         <v>95</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>83</v>
@@ -7391,7 +7398,7 @@
         <v>83</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>81</v>
@@ -7412,10 +7419,10 @@
         <v>83</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>83</v>
@@ -7426,10 +7433,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7452,13 +7459,13 @@
         <v>83</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -7509,7 +7516,7 @@
         <v>83</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>81</v>
@@ -7533,7 +7540,7 @@
         <v>83</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>83</v>
@@ -7544,10 +7551,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7576,7 +7583,7 @@
         <v>141</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="N45" t="s" s="2">
         <v>143</v>
@@ -7617,19 +7624,19 @@
         <v>83</v>
       </c>
       <c r="AB45" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="AC45" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="AD45" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE45" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
@@ -7653,7 +7660,7 @@
         <v>83</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>83</v>
@@ -7664,10 +7671,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7693,23 +7700,23 @@
         <v>108</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q46" s="2"/>
       <c r="R46" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="S46" t="s" s="2">
         <v>83</v>
@@ -7751,7 +7758,7 @@
         <v>83</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
@@ -7772,10 +7779,10 @@
         <v>83</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>83</v>
@@ -7786,10 +7793,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7812,16 +7819,16 @@
         <v>95</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7871,7 +7878,7 @@
         <v>83</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
@@ -7892,10 +7899,10 @@
         <v>83</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>83</v>
@@ -7906,10 +7913,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7935,14 +7942,14 @@
         <v>114</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>83</v>
@@ -7991,7 +7998,7 @@
         <v>83</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>81</v>
@@ -8012,10 +8019,10 @@
         <v>83</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>83</v>
@@ -8026,10 +8033,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8052,17 +8059,17 @@
         <v>95</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>83</v>
@@ -8111,7 +8118,7 @@
         <v>83</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
@@ -8132,10 +8139,10 @@
         <v>83</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>83</v>
@@ -8146,10 +8153,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8172,19 +8179,19 @@
         <v>95</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>83</v>
@@ -8233,7 +8240,7 @@
         <v>83</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
@@ -8254,10 +8261,10 @@
         <v>83</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>83</v>
@@ -8268,10 +8275,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8294,19 +8301,19 @@
         <v>95</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>83</v>
@@ -8355,7 +8362,7 @@
         <v>83</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -8376,10 +8383,10 @@
         <v>83</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>83</v>
@@ -8390,14 +8397,14 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -8419,16 +8426,16 @@
         <v>190</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>83</v>
@@ -8453,13 +8460,13 @@
         <v>83</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>83</v>
@@ -8477,7 +8484,7 @@
         <v>83</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>94</v>
@@ -8492,30 +8499,30 @@
         <v>106</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8538,13 +8545,13 @@
         <v>83</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8595,7 +8602,7 @@
         <v>83</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -8619,7 +8626,7 @@
         <v>83</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>83</v>
@@ -8630,10 +8637,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8662,7 +8669,7 @@
         <v>141</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="N54" t="s" s="2">
         <v>143</v>
@@ -8703,19 +8710,19 @@
         <v>83</v>
       </c>
       <c r="AB54" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="AC54" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="AD54" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE54" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -8739,7 +8746,7 @@
         <v>83</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>83</v>
@@ -8750,10 +8757,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8776,19 +8783,19 @@
         <v>95</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>83</v>
@@ -8825,17 +8832,17 @@
         <v>83</v>
       </c>
       <c r="AB55" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="AC55" s="2"/>
       <c r="AD55" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE55" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -8856,10 +8863,10 @@
         <v>83</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>83</v>
@@ -8870,13 +8877,13 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="C56" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="D56" t="s" s="2">
         <v>83</v>
@@ -8898,19 +8905,19 @@
         <v>95</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>83</v>
@@ -8939,7 +8946,7 @@
       </c>
       <c r="Y56" s="2"/>
       <c r="Z56" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>83</v>
@@ -8957,7 +8964,7 @@
         <v>83</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
@@ -8978,10 +8985,10 @@
         <v>83</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>83</v>
@@ -8992,10 +8999,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9018,13 +9025,13 @@
         <v>83</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -9075,7 +9082,7 @@
         <v>83</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>81</v>
@@ -9099,7 +9106,7 @@
         <v>83</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>83</v>
@@ -9110,10 +9117,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9142,7 +9149,7 @@
         <v>141</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="N58" t="s" s="2">
         <v>143</v>
@@ -9183,19 +9190,19 @@
         <v>83</v>
       </c>
       <c r="AB58" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="AC58" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="AD58" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE58" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -9219,7 +9226,7 @@
         <v>83</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>83</v>
@@ -9230,10 +9237,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9259,23 +9266,23 @@
         <v>108</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q59" s="2"/>
       <c r="R59" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="S59" t="s" s="2">
         <v>83</v>
@@ -9317,7 +9324,7 @@
         <v>83</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -9338,10 +9345,10 @@
         <v>83</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>83</v>
@@ -9352,10 +9359,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9378,16 +9385,16 @@
         <v>95</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -9437,7 +9444,7 @@
         <v>83</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
@@ -9458,10 +9465,10 @@
         <v>83</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>83</v>
@@ -9472,10 +9479,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9501,14 +9508,14 @@
         <v>114</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>83</v>
@@ -9557,7 +9564,7 @@
         <v>83</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
@@ -9578,10 +9585,10 @@
         <v>83</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>83</v>
@@ -9592,10 +9599,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9618,17 +9625,17 @@
         <v>95</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>83</v>
@@ -9677,7 +9684,7 @@
         <v>83</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
@@ -9698,10 +9705,10 @@
         <v>83</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>83</v>
@@ -9712,10 +9719,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9738,19 +9745,19 @@
         <v>95</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>83</v>
@@ -9799,7 +9806,7 @@
         <v>83</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>81</v>
@@ -9820,10 +9827,10 @@
         <v>83</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>83</v>
@@ -9834,13 +9841,13 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="C64" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="D64" t="s" s="2">
         <v>83</v>
@@ -9862,19 +9869,19 @@
         <v>95</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>83</v>
@@ -9903,7 +9910,7 @@
       </c>
       <c r="Y64" s="2"/>
       <c r="Z64" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>83</v>
@@ -9921,7 +9928,7 @@
         <v>83</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
@@ -9942,10 +9949,10 @@
         <v>83</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>83</v>
@@ -9956,10 +9963,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9982,13 +9989,13 @@
         <v>83</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -10039,7 +10046,7 @@
         <v>83</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>81</v>
@@ -10063,7 +10070,7 @@
         <v>83</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>83</v>
@@ -10074,10 +10081,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10106,7 +10113,7 @@
         <v>141</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="N66" t="s" s="2">
         <v>143</v>
@@ -10147,19 +10154,19 @@
         <v>83</v>
       </c>
       <c r="AB66" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="AC66" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="AD66" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE66" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>81</v>
@@ -10183,7 +10190,7 @@
         <v>83</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>83</v>
@@ -10194,10 +10201,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10223,23 +10230,23 @@
         <v>108</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q67" s="2"/>
       <c r="R67" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="S67" t="s" s="2">
         <v>83</v>
@@ -10281,7 +10288,7 @@
         <v>83</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>81</v>
@@ -10302,10 +10309,10 @@
         <v>83</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>83</v>
@@ -10316,10 +10323,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10342,16 +10349,16 @@
         <v>95</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -10401,7 +10408,7 @@
         <v>83</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>81</v>
@@ -10422,10 +10429,10 @@
         <v>83</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>83</v>
@@ -10436,10 +10443,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10465,14 +10472,14 @@
         <v>114</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>83</v>
@@ -10521,7 +10528,7 @@
         <v>83</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>81</v>
@@ -10542,10 +10549,10 @@
         <v>83</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>83</v>
@@ -10556,10 +10563,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10582,17 +10589,17 @@
         <v>95</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>83</v>
@@ -10641,7 +10648,7 @@
         <v>83</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>81</v>
@@ -10662,10 +10669,10 @@
         <v>83</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>83</v>
@@ -10676,10 +10683,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10702,19 +10709,19 @@
         <v>95</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>83</v>
@@ -10763,7 +10770,7 @@
         <v>83</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>81</v>
@@ -10784,10 +10791,10 @@
         <v>83</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>83</v>
@@ -10798,13 +10805,13 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="C72" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="D72" t="s" s="2">
         <v>83</v>
@@ -10826,19 +10833,19 @@
         <v>95</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>83</v>
@@ -10867,7 +10874,7 @@
       </c>
       <c r="Y72" s="2"/>
       <c r="Z72" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>83</v>
@@ -10885,7 +10892,7 @@
         <v>83</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>81</v>
@@ -10906,10 +10913,10 @@
         <v>83</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>83</v>
@@ -10920,10 +10927,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10946,13 +10953,13 @@
         <v>83</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -11003,7 +11010,7 @@
         <v>83</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>81</v>
@@ -11027,7 +11034,7 @@
         <v>83</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>83</v>
@@ -11038,10 +11045,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11070,7 +11077,7 @@
         <v>141</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="N74" t="s" s="2">
         <v>143</v>
@@ -11111,19 +11118,19 @@
         <v>83</v>
       </c>
       <c r="AB74" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="AC74" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="AD74" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE74" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>81</v>
@@ -11147,7 +11154,7 @@
         <v>83</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>83</v>
@@ -11158,10 +11165,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11187,23 +11194,23 @@
         <v>108</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q75" s="2"/>
       <c r="R75" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="S75" t="s" s="2">
         <v>83</v>
@@ -11245,7 +11252,7 @@
         <v>83</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>81</v>
@@ -11266,10 +11273,10 @@
         <v>83</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>83</v>
@@ -11280,10 +11287,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11306,16 +11313,16 @@
         <v>95</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -11365,7 +11372,7 @@
         <v>83</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>81</v>
@@ -11386,10 +11393,10 @@
         <v>83</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>83</v>
@@ -11400,10 +11407,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11429,14 +11436,14 @@
         <v>114</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>83</v>
@@ -11485,7 +11492,7 @@
         <v>83</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>81</v>
@@ -11506,10 +11513,10 @@
         <v>83</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>83</v>
@@ -11520,10 +11527,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11546,17 +11553,17 @@
         <v>95</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>83</v>
@@ -11605,7 +11612,7 @@
         <v>83</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>81</v>
@@ -11626,10 +11633,10 @@
         <v>83</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>83</v>
@@ -11640,10 +11647,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11666,19 +11673,19 @@
         <v>95</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="O79" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>83</v>
@@ -11727,7 +11734,7 @@
         <v>83</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>81</v>
@@ -11748,10 +11755,10 @@
         <v>83</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>83</v>
@@ -11762,10 +11769,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11788,19 +11795,19 @@
         <v>95</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="O80" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>83</v>
@@ -11849,7 +11856,7 @@
         <v>83</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>81</v>
@@ -11870,10 +11877,10 @@
         <v>83</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>83</v>
@@ -11884,10 +11891,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11910,19 +11917,19 @@
         <v>95</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="O81" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>83</v>
@@ -11971,7 +11978,7 @@
         <v>83</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>81</v>
@@ -11986,19 +11993,19 @@
         <v>106</v>
       </c>
       <c r="AK81" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="AL81" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="AO81" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AP81" t="s" s="2">
         <v>83</v>
@@ -12006,10 +12013,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12032,16 +12039,16 @@
         <v>95</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
@@ -12091,7 +12098,7 @@
         <v>83</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>81</v>
@@ -12112,13 +12119,13 @@
         <v>83</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="AO82" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AP82" t="s" s="2">
         <v>83</v>
@@ -12126,14 +12133,14 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
@@ -12152,19 +12159,19 @@
         <v>95</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="O83" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>83</v>
@@ -12213,7 +12220,7 @@
         <v>83</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>81</v>
@@ -12228,19 +12235,19 @@
         <v>106</v>
       </c>
       <c r="AK83" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="AL83" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="AO83" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="AP83" t="s" s="2">
         <v>83</v>
@@ -12248,14 +12255,14 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
@@ -12274,19 +12281,19 @@
         <v>95</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>83</v>
@@ -12335,7 +12342,7 @@
         <v>83</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>81</v>
@@ -12350,19 +12357,19 @@
         <v>106</v>
       </c>
       <c r="AK84" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="AL84" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="AO84" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="AP84" t="s" s="2">
         <v>83</v>
@@ -12370,10 +12377,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12396,16 +12403,16 @@
         <v>95</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -12455,7 +12462,7 @@
         <v>83</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>81</v>
@@ -12476,13 +12483,13 @@
         <v>83</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="AO85" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="AP85" t="s" s="2">
         <v>83</v>
@@ -12490,10 +12497,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12516,19 +12523,19 @@
         <v>95</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="O86" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>83</v>
@@ -12577,7 +12584,7 @@
         <v>83</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>81</v>
@@ -12592,19 +12599,19 @@
         <v>106</v>
       </c>
       <c r="AK86" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="AL86" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="AO86" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="AP86" t="s" s="2">
         <v>83</v>
@@ -12612,10 +12619,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12638,19 +12645,19 @@
         <v>95</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="O87" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>83</v>
@@ -12699,7 +12706,7 @@
         <v>83</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>81</v>
@@ -12708,7 +12715,7 @@
         <v>94</v>
       </c>
       <c r="AI87" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="AJ87" t="s" s="2">
         <v>106</v>
@@ -12717,27 +12724,27 @@
         <v>83</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP87" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12763,16 +12770,16 @@
         <v>190</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="O88" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>83</v>
@@ -12797,13 +12804,13 @@
         <v>83</v>
       </c>
       <c r="X88" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="Y88" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="Z88" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="AA88" t="s" s="2">
         <v>83</v>
@@ -12821,7 +12828,7 @@
         <v>83</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>81</v>
@@ -12830,7 +12837,7 @@
         <v>94</v>
       </c>
       <c r="AI88" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="AJ88" t="s" s="2">
         <v>106</v>
@@ -12845,7 +12852,7 @@
         <v>137</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>83</v>
@@ -12856,14 +12863,14 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
@@ -12885,16 +12892,16 @@
         <v>190</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="O89" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>83</v>
@@ -12919,13 +12926,13 @@
         <v>83</v>
       </c>
       <c r="X89" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="Y89" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="Z89" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="AA89" t="s" s="2">
         <v>83</v>
@@ -12943,7 +12950,7 @@
         <v>83</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>81</v>
@@ -12961,27 +12968,27 @@
         <v>83</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP89" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13004,19 +13011,19 @@
         <v>83</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="O90" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>83</v>
@@ -13065,7 +13072,7 @@
         <v>83</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>81</v>
@@ -13086,10 +13093,10 @@
         <v>83</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>83</v>
@@ -13100,10 +13107,10 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13129,13 +13136,13 @@
         <v>190</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
@@ -13161,13 +13168,11 @@
         <v>83</v>
       </c>
       <c r="X91" t="s" s="2">
-        <v>323</v>
-      </c>
-      <c r="Y91" t="s" s="2">
-        <v>474</v>
-      </c>
+        <v>325</v>
+      </c>
+      <c r="Y91" s="2"/>
       <c r="Z91" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>83</v>
@@ -13185,7 +13190,7 @@
         <v>83</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>81</v>
@@ -13203,27 +13208,27 @@
         <v>83</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP91" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13249,16 +13254,16 @@
         <v>190</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="O92" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>83</v>
@@ -13283,13 +13288,13 @@
         <v>83</v>
       </c>
       <c r="X92" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="Y92" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="Z92" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>83</v>
@@ -13307,7 +13312,7 @@
         <v>83</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>81</v>
@@ -13328,10 +13333,10 @@
         <v>83</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>83</v>
@@ -13342,10 +13347,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13368,16 +13373,16 @@
         <v>83</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
@@ -13427,7 +13432,7 @@
         <v>83</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>81</v>
@@ -13445,27 +13450,27 @@
         <v>83</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP93" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13488,16 +13493,16 @@
         <v>83</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
@@ -13547,7 +13552,7 @@
         <v>83</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>81</v>
@@ -13565,27 +13570,27 @@
         <v>83</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP94" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13608,19 +13613,19 @@
         <v>83</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="O95" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>83</v>
@@ -13669,7 +13674,7 @@
         <v>83</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>81</v>
@@ -13681,7 +13686,7 @@
         <v>83</v>
       </c>
       <c r="AJ95" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="AK95" t="s" s="2">
         <v>83</v>
@@ -13690,10 +13695,10 @@
         <v>83</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>83</v>
@@ -13704,10 +13709,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13730,13 +13735,13 @@
         <v>83</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
@@ -13787,7 +13792,7 @@
         <v>83</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>81</v>
@@ -13811,7 +13816,7 @@
         <v>83</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="AO96" t="s" s="2">
         <v>83</v>
@@ -13822,10 +13827,10 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13854,7 +13859,7 @@
         <v>141</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="N97" t="s" s="2">
         <v>143</v>
@@ -13907,7 +13912,7 @@
         <v>83</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>81</v>
@@ -13931,7 +13936,7 @@
         <v>83</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="AO97" t="s" s="2">
         <v>83</v>
@@ -13942,14 +13947,14 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="E98" s="2"/>
       <c r="F98" t="s" s="2">
@@ -13971,10 +13976,10 @@
         <v>140</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="N98" t="s" s="2">
         <v>143</v>
@@ -14029,7 +14034,7 @@
         <v>83</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>81</v>
@@ -14064,10 +14069,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14090,13 +14095,13 @@
         <v>83</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" s="2"/>
@@ -14147,7 +14152,7 @@
         <v>83</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>81</v>
@@ -14156,7 +14161,7 @@
         <v>94</v>
       </c>
       <c r="AI99" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="AJ99" t="s" s="2">
         <v>106</v>
@@ -14168,10 +14173,10 @@
         <v>83</v>
       </c>
       <c r="AM99" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="AN99" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="AO99" t="s" s="2">
         <v>83</v>
@@ -14182,10 +14187,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14208,13 +14213,13 @@
         <v>83</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" s="2"/>
@@ -14265,7 +14270,7 @@
         <v>83</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>81</v>
@@ -14274,7 +14279,7 @@
         <v>94</v>
       </c>
       <c r="AI100" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="AJ100" t="s" s="2">
         <v>106</v>
@@ -14286,10 +14291,10 @@
         <v>83</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="AO100" t="s" s="2">
         <v>83</v>
@@ -14300,10 +14305,10 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14329,16 +14334,16 @@
         <v>190</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="O101" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>83</v>
@@ -14366,10 +14371,10 @@
         <v>118</v>
       </c>
       <c r="Y101" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="Z101" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="AA101" t="s" s="2">
         <v>83</v>
@@ -14387,7 +14392,7 @@
         <v>83</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>81</v>
@@ -14405,13 +14410,13 @@
         <v>83</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="AO101" t="s" s="2">
         <v>83</v>
@@ -14422,10 +14427,10 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14451,16 +14456,16 @@
         <v>190</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="O102" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>83</v>
@@ -14485,13 +14490,13 @@
         <v>83</v>
       </c>
       <c r="X102" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="Y102" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="Z102" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="AA102" t="s" s="2">
         <v>83</v>
@@ -14509,7 +14514,7 @@
         <v>83</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>81</v>
@@ -14527,13 +14532,13 @@
         <v>83</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="AO102" t="s" s="2">
         <v>83</v>
@@ -14544,10 +14549,10 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14570,17 +14575,17 @@
         <v>83</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>83</v>
@@ -14629,7 +14634,7 @@
         <v>83</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>81</v>
@@ -14653,7 +14658,7 @@
         <v>83</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="AO103" t="s" s="2">
         <v>83</v>
@@ -14664,10 +14669,10 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14690,13 +14695,13 @@
         <v>83</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" s="2"/>
@@ -14747,7 +14752,7 @@
         <v>83</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>81</v>
@@ -14768,10 +14773,10 @@
         <v>83</v>
       </c>
       <c r="AM104" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="AO104" t="s" s="2">
         <v>83</v>
@@ -14782,10 +14787,10 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14808,16 +14813,16 @@
         <v>95</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
@@ -14867,7 +14872,7 @@
         <v>83</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>81</v>
@@ -14888,10 +14893,10 @@
         <v>83</v>
       </c>
       <c r="AM105" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="AN105" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="AO105" t="s" s="2">
         <v>83</v>
@@ -14902,10 +14907,10 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14928,16 +14933,16 @@
         <v>95</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="O106" s="2"/>
       <c r="P106" t="s" s="2">
@@ -14987,7 +14992,7 @@
         <v>83</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>81</v>
@@ -15008,10 +15013,10 @@
         <v>83</v>
       </c>
       <c r="AM106" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="AN106" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="AO106" t="s" s="2">
         <v>83</v>
@@ -15022,10 +15027,10 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15048,19 +15053,19 @@
         <v>95</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="O107" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="P107" t="s" s="2">
         <v>83</v>
@@ -15109,7 +15114,7 @@
         <v>83</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>81</v>
@@ -15130,10 +15135,10 @@
         <v>83</v>
       </c>
       <c r="AM107" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="AN107" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="AO107" t="s" s="2">
         <v>83</v>
@@ -15144,10 +15149,10 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15170,13 +15175,13 @@
         <v>83</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="N108" s="2"/>
       <c r="O108" s="2"/>
@@ -15227,7 +15232,7 @@
         <v>83</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>81</v>
@@ -15251,7 +15256,7 @@
         <v>83</v>
       </c>
       <c r="AN108" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="AO108" t="s" s="2">
         <v>83</v>
@@ -15262,10 +15267,10 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15294,7 +15299,7 @@
         <v>141</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="N109" t="s" s="2">
         <v>143</v>
@@ -15347,7 +15352,7 @@
         <v>83</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>81</v>
@@ -15371,7 +15376,7 @@
         <v>83</v>
       </c>
       <c r="AN109" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="AO109" t="s" s="2">
         <v>83</v>
@@ -15382,14 +15387,14 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="E110" s="2"/>
       <c r="F110" t="s" s="2">
@@ -15411,10 +15416,10 @@
         <v>140</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="N110" t="s" s="2">
         <v>143</v>
@@ -15469,7 +15474,7 @@
         <v>83</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>81</v>
@@ -15504,10 +15509,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15533,16 +15538,16 @@
         <v>190</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="O111" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>83</v>
@@ -15567,13 +15572,13 @@
         <v>83</v>
       </c>
       <c r="X111" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="Y111" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="Z111" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="AA111" t="s" s="2">
         <v>83</v>
@@ -15591,7 +15596,7 @@
         <v>83</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>94</v>
@@ -15609,16 +15614,16 @@
         <v>83</v>
       </c>
       <c r="AL111" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="AM111" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="AN111" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="AO111" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="AP111" t="s" s="2">
         <v>83</v>
@@ -15626,10 +15631,10 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -15652,19 +15657,19 @@
         <v>95</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="N112" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="O112" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="P112" t="s" s="2">
         <v>83</v>
@@ -15713,7 +15718,7 @@
         <v>83</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>81</v>
@@ -15731,27 +15736,27 @@
         <v>83</v>
       </c>
       <c r="AL112" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="AM112" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="AN112" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="AO112" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP112" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -15777,16 +15782,16 @@
         <v>190</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="O113" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="P113" t="s" s="2">
         <v>83</v>
@@ -15811,13 +15816,13 @@
         <v>83</v>
       </c>
       <c r="X113" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="Y113" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="Z113" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="AA113" t="s" s="2">
         <v>83</v>
@@ -15835,7 +15840,7 @@
         <v>83</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>81</v>
@@ -15844,7 +15849,7 @@
         <v>94</v>
       </c>
       <c r="AI113" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="AJ113" t="s" s="2">
         <v>106</v>
@@ -15859,7 +15864,7 @@
         <v>137</v>
       </c>
       <c r="AN113" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="AO113" t="s" s="2">
         <v>83</v>
@@ -15870,14 +15875,14 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="E114" s="2"/>
       <c r="F114" t="s" s="2">
@@ -15899,16 +15904,16 @@
         <v>190</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="N114" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="O114" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="P114" t="s" s="2">
         <v>83</v>
@@ -15933,13 +15938,13 @@
         <v>83</v>
       </c>
       <c r="X114" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="Y114" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="Z114" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="AA114" t="s" s="2">
         <v>83</v>
@@ -15957,7 +15962,7 @@
         <v>83</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>81</v>
@@ -15975,27 +15980,27 @@
         <v>83</v>
       </c>
       <c r="AL114" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="AM114" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="AN114" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="AO114" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP114" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -16021,16 +16026,16 @@
         <v>84</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="N115" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="O115" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="P115" t="s" s="2">
         <v>83</v>
@@ -16079,7 +16084,7 @@
         <v>83</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>81</v>
@@ -16100,10 +16105,10 @@
         <v>83</v>
       </c>
       <c r="AM115" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="AN115" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AO115" t="s" s="2">
         <v>83</v>
